--- a/output/pdf_financials_xlsx/EDW.H.xlsx
+++ b/output/pdf_financials_xlsx/EDW.H.xlsx
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.298044</v>
+        <v>-0.298044</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3.338003</v>
+        <v>-3.338003</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.318985</v>
+        <v>-3.318985</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.298044</v>
+        <v>-0.298044</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3.338003</v>
+        <v>-3.338003</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.318985</v>
+        <v>-3.318985</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.298044</v>
+        <v>-0.298044</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3.338003</v>
+        <v>-3.338003</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.318985</v>
+        <v>-3.318985</v>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>14.9022</v>
+        <v>-14.9022</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>30.345482</v>
+        <v>-30.345482</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>55.316417</v>
+        <v>-55.316417</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.298044</v>
+        <v>-0.298044</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.380339</v>
+        <v>-3.295667</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.537577</v>
+        <v>-3.100393</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.298044</v>
+        <v>-0.298044</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.380339</v>
+        <v>-3.295667</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.537577</v>
+        <v>-3.100393</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -4613,34 +4613,34 @@
         <v>0.278359</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>5.632502</v>
+        <v>0.278359</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>9.144311</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>10.216068</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>10.679108</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>11.129105</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>11.175539</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>11.272318</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>11.542501</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>11.542501</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>11.542501</v>
       </c>
     </row>
     <row r="93">
@@ -7494,7 +7494,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -7555,7 +7559,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -8432,7 +8440,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -8495,7 +8507,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -10078,7 +10094,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -10145,7 +10165,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -16831,7 +16855,11 @@
           <t>Share-based payments reserve 3,299,403 1,487,121</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -16902,7 +16930,11 @@
           <t>Warrants reserve 5,844,908 4,522,666</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -26073,10 +26105,10 @@
         </is>
       </c>
       <c r="F271" s="5" t="n">
-        <v>3.338003</v>
+        <v>-3.338003</v>
       </c>
       <c r="G271" s="5" t="n">
-        <v>3.318985</v>
+        <v>-3.318985</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -26217,10 +26249,10 @@
         </is>
       </c>
       <c r="F273" s="5" t="n">
-        <v>3.338003</v>
+        <v>-3.338003</v>
       </c>
       <c r="G273" s="5" t="n">
-        <v>3.681108</v>
+        <v>-3.681108</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -27717,10 +27749,10 @@
         </is>
       </c>
       <c r="E294" s="5" t="n">
-        <v>0.298044</v>
+        <v>-0.298044</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>2.838856</v>
+        <v>-2.838856</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EDW.H.xlsx
+++ b/output/pdf_financials_xlsx/EDW.H.xlsx
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000752</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>-0.042336</v>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.298044</v>
+        <v>-0.297292</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-3.295667</v>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.298044</v>
+        <v>-0.297292</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-3.295667</v>
@@ -2187,34 +2187,34 @@
         <v>0.810029</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>5.099109</v>
+        <v>0.810029</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.550428</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.962326</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.375462</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.24953</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.160455</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.387074</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.650066</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.51066</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.43417</v>
       </c>
     </row>
     <row r="35">
@@ -2267,34 +2267,34 @@
         <v>0.810029</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>15.099109</v>
+        <v>10.810029</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.9</v>
+        <v>5.450428</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.854519</v>
+        <v>3.816845</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.38</v>
+        <v>0.755462</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.19</v>
+        <v>0.43953</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.14</v>
+        <v>0.300455</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.015</v>
+        <v>0.402074</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.06</v>
+        <v>1.710066</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.718</v>
+        <v>1.22866</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.5157659999999999</v>
+        <v>0.949936</v>
       </c>
     </row>
     <row r="37">
@@ -2750,31 +2750,31 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.743885</v>
+        <v>0.193457</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.085903</v>
+        <v>0.123577</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.301215</v>
+        <v>0.051685</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.203585</v>
+        <v>0.04313</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.444842</v>
+        <v>0.057768</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.676504</v>
+        <v>0.026438</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.538295</v>
+        <v>0.027635</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.46107</v>
+        <v>0.0269</v>
       </c>
     </row>
     <row r="49">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9122,7 +9122,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -12005,7 +12009,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -13265,7 +13273,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -14466,7 +14478,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -15671,7 +15683,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -16192,7 +16204,11 @@
           <t>Reclamation deposits 6 2,516,382 2,526,484</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -27672,7 +27688,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E293" s="5" t="n">
